--- a/artfynd/A 42633-2025 artfynd.xlsx
+++ b/artfynd/A 42633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111287368</v>
       </c>
       <c r="B2" t="n">
-        <v>89665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523569.2893025596</v>
+        <v>523569</v>
       </c>
       <c r="R2" t="n">
-        <v>6619672.686347006</v>
+        <v>6619673</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,19 +754,9 @@
           <t>2021-07-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111256731</v>
+        <v>111929729</v>
       </c>
       <c r="B3" t="n">
-        <v>90151</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,52 +795,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bornsviken, Ramsbergs sn, Vstm</t>
+          <t>Bornsviken, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523574.6029847446</v>
+        <v>523536</v>
       </c>
       <c r="R3" t="n">
-        <v>6619711.567858044</v>
+        <v>6619704</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,26 +869,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>gammal låga</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula # gammal låga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -947,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111929729</v>
+        <v>111256731</v>
       </c>
       <c r="B4" t="n">
-        <v>89813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,40 +896,52 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bornsviken, Vstm</t>
+          <t>Bornsviken, Ramsbergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523536</v>
+        <v>523575</v>
       </c>
       <c r="R4" t="n">
-        <v>6619704</v>
+        <v>6619712</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,12 +965,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,6 +982,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>gammal låga</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula # gammal låga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1053,15 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112279873</v>
+        <v>112280232</v>
       </c>
       <c r="B5" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,33 +1029,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>4404</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1104,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523481</v>
+        <v>523440</v>
       </c>
       <c r="R5" t="n">
-        <v>6619795</v>
+        <v>6619756</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1167,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112299136</v>
+        <v>112280476</v>
       </c>
       <c r="B6" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,33 +1130,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4404</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1218,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523459</v>
+        <v>523483</v>
       </c>
       <c r="R6" t="n">
-        <v>6619798</v>
+        <v>6619644</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,12 +1187,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,41 +1220,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112792096</v>
+        <v>112792184</v>
       </c>
       <c r="B7" t="n">
-        <v>90554</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6031</v>
+        <v>4404</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523489</v>
+        <v>523470</v>
       </c>
       <c r="R7" t="n">
-        <v>6619760</v>
+        <v>6619801</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1387,69 +1329,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115776193</v>
+        <v>112279873</v>
       </c>
       <c r="B8" t="n">
-        <v>57220</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103060</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brun glada</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Milvus migrans</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>sträckande</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bornsviken, Ramsbergs sn, Vstm</t>
+          <t>Bornsviken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523575</v>
+        <v>523481</v>
       </c>
       <c r="R8" t="n">
-        <v>6619712</v>
+        <v>6619795</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,22 +1405,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,6 +1419,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1512,6 +1435,418 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112279547</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>523438</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6619852</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112299136</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>523459</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6619798</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112792164</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>523437</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6619842</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112792096</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>523489</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6619760</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42633-2025 artfynd.xlsx
+++ b/artfynd/A 42633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111287368</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111929729</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111256731</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280232</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280476</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792184</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112279873</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112279547</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299136</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,6 +1796,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792164</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1847,8 +1902,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792096</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>